--- a/After_Included.xlsx
+++ b/After_Included.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="78">
   <si>
     <t>multivalues</t>
   </si>
@@ -115,76 +115,139 @@
     <t>Used_Fallback_HeadVolume</t>
   </si>
   <si>
-    <t>CC(2.2)+</t>
-  </si>
-  <si>
-    <t>226CC(2.2)+includedexcluded</t>
-  </si>
-  <si>
-    <t>226</t>
-  </si>
-  <si>
-    <t>522582300</t>
-  </si>
-  <si>
-    <t>FIAPE</t>
+    <t>CMB(ALC)+</t>
+  </si>
+  <si>
+    <t>CMB(ALC,GA)+,PC(CA79)+</t>
+  </si>
+  <si>
+    <t>CMB(ALC,GA)+</t>
+  </si>
+  <si>
+    <t>CMB(ALC,GA)+,PC(C513)+</t>
+  </si>
+  <si>
+    <t>359CMB(ALC)+includedexcluded</t>
+  </si>
+  <si>
+    <t>359CMB(ALC,GA)+,PC(CA79)+includedexcluded</t>
+  </si>
+  <si>
+    <t>359CMB(ALC,GA)+includedexcluded</t>
+  </si>
+  <si>
+    <t>359CMB(ALC,GA)+,PC(C513)+includedexcluded</t>
+  </si>
+  <si>
+    <t>358CMB(ALC)+includedexcluded</t>
+  </si>
+  <si>
+    <t>359</t>
+  </si>
+  <si>
+    <t>358</t>
+  </si>
+  <si>
+    <t>522391460</t>
+  </si>
+  <si>
+    <t>522229500</t>
+  </si>
+  <si>
+    <t>465376850</t>
+  </si>
+  <si>
+    <t>519840640</t>
+  </si>
+  <si>
+    <t>FAASA</t>
+  </si>
+  <si>
+    <t>FIASA</t>
   </si>
   <si>
     <t>None</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>5TK</t>
-  </si>
-  <si>
-    <t>3RU</t>
-  </si>
-  <si>
-    <t>5S9</t>
-  </si>
-  <si>
-    <t>5RT</t>
-  </si>
-  <si>
-    <t>2WW</t>
-  </si>
-  <si>
-    <t>2T0</t>
-  </si>
-  <si>
-    <t>5WT</t>
-  </si>
-  <si>
-    <t>2S0</t>
-  </si>
-  <si>
-    <t>3RW</t>
-  </si>
-  <si>
-    <t>5R9</t>
-  </si>
-  <si>
-    <t>3SW</t>
-  </si>
-  <si>
-    <t>5P9</t>
-  </si>
-  <si>
-    <t>5ST</t>
-  </si>
-  <si>
-    <t>3PU</t>
-  </si>
-  <si>
-    <t>2.2</t>
-  </si>
-  <si>
-    <t>1.3</t>
-  </si>
-  <si>
-    <t>Cilindrata (l)</t>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>ATH</t>
+  </si>
+  <si>
+    <t>AF2</t>
+  </si>
+  <si>
+    <t>AFU</t>
+  </si>
+  <si>
+    <t>AL2</t>
+  </si>
+  <si>
+    <t>AFV</t>
+  </si>
+  <si>
+    <t>AHK</t>
+  </si>
+  <si>
+    <t>AFK</t>
+  </si>
+  <si>
+    <t>AHV</t>
+  </si>
+  <si>
+    <t>AGB</t>
+  </si>
+  <si>
+    <t>AGK</t>
+  </si>
+  <si>
+    <t>ACS</t>
+  </si>
+  <si>
+    <t>AA2</t>
+  </si>
+  <si>
+    <t>AGU</t>
+  </si>
+  <si>
+    <t>AFB</t>
+  </si>
+  <si>
+    <t>AG2</t>
+  </si>
+  <si>
+    <t>ATS</t>
+  </si>
+  <si>
+    <t>alcool</t>
+  </si>
+  <si>
+    <t>alcool,cvt,flex</t>
+  </si>
+  <si>
+    <t>alcool,flex</t>
+  </si>
+  <si>
+    <t>alcool,c513,flex</t>
+  </si>
+  <si>
+    <t>benzina,flex</t>
+  </si>
+  <si>
+    <t>benzina,c513</t>
+  </si>
+  <si>
+    <t>benzina</t>
+  </si>
+  <si>
+    <t>benzina,cvt</t>
+  </si>
+  <si>
+    <t>Carburante</t>
+  </si>
+  <si>
+    <t>Carburante,Famiglia Cambio</t>
   </si>
 </sst>
 </file>
@@ -542,7 +605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AG15"/>
+  <dimension ref="A1:AG43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:33">
@@ -651,37 +714,37 @@
         <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="I2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="J2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="K2">
-        <v>350</v>
+        <v>16887</v>
       </c>
       <c r="L2">
-        <v>62000</v>
+        <v>92722</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -690,58 +753,58 @@
         <v>33</v>
       </c>
       <c r="O2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="R2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="S2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="U2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="V2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="W2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="X2">
-        <v>350</v>
+        <v>16887</v>
       </c>
       <c r="Y2">
-        <v>62000</v>
+        <v>92722</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="AB2" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="AC2" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>16887</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>16887</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -752,37 +815,37 @@
         <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="I3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="J3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="K3">
-        <v>17600</v>
+        <v>19870</v>
       </c>
       <c r="L3">
-        <v>62000</v>
+        <v>92722</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -791,58 +854,58 @@
         <v>33</v>
       </c>
       <c r="O3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="R3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="S3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="U3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="V3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="W3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="X3">
-        <v>17600</v>
+        <v>19870</v>
       </c>
       <c r="Y3">
-        <v>62000</v>
+        <v>92722</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="AB3" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="AC3" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>19870</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>19870</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -853,37 +916,37 @@
         <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G4" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="I4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="J4" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="K4">
-        <v>1400</v>
+        <v>19702</v>
       </c>
       <c r="L4">
-        <v>62000</v>
+        <v>92722</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -892,58 +955,58 @@
         <v>33</v>
       </c>
       <c r="O4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P4" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q4" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="R4" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="S4" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T4" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="U4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="V4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="W4" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="X4">
-        <v>1400</v>
+        <v>19702</v>
       </c>
       <c r="Y4">
-        <v>62000</v>
+        <v>92722</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AA4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="AB4" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="AC4" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="AD4">
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>19702</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>19702</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -954,37 +1017,37 @@
         <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="I5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="J5" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="K5">
-        <v>600</v>
+        <v>2138</v>
       </c>
       <c r="L5">
-        <v>62000</v>
+        <v>92722</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -993,58 +1056,58 @@
         <v>33</v>
       </c>
       <c r="O5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q5" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="R5" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="S5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="U5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="V5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="W5" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="X5">
-        <v>600</v>
+        <v>2138</v>
       </c>
       <c r="Y5">
-        <v>62000</v>
+        <v>92722</v>
       </c>
       <c r="Z5">
         <v>0</v>
       </c>
       <c r="AA5" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="AB5" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="AC5" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="AD5">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>2138</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2138</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1055,37 +1118,37 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="I6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="J6" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="K6">
-        <v>8800</v>
+        <v>11258</v>
       </c>
       <c r="L6">
-        <v>62000</v>
+        <v>92722</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -1094,58 +1157,58 @@
         <v>33</v>
       </c>
       <c r="O6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P6" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q6" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="R6" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="S6" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T6" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="U6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="V6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="W6" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="X6">
-        <v>8800</v>
+        <v>11258</v>
       </c>
       <c r="Y6">
-        <v>62000</v>
+        <v>92722</v>
       </c>
       <c r="Z6">
         <v>0</v>
       </c>
       <c r="AA6" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="AB6" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="AC6" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="AD6">
-        <v>8800</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>11258</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>11258</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1156,37 +1219,37 @@
         <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H7" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="I7" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="J7" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="K7">
-        <v>4400</v>
+        <v>10650</v>
       </c>
       <c r="L7">
-        <v>62000</v>
+        <v>92722</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -1195,58 +1258,58 @@
         <v>33</v>
       </c>
       <c r="O7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P7" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q7" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="R7" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="S7" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T7" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="U7" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="V7" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="W7" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="X7">
-        <v>4400</v>
+        <v>10650</v>
       </c>
       <c r="Y7">
-        <v>62000</v>
+        <v>92722</v>
       </c>
       <c r="Z7">
         <v>0</v>
       </c>
       <c r="AA7" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="AB7" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="AC7" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="AD7">
         <v>0</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>10650</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>10650</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1257,37 +1320,37 @@
         <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H8" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="I8" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="J8" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="K8">
-        <v>300</v>
+        <v>3773</v>
       </c>
       <c r="L8">
-        <v>62000</v>
+        <v>92722</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -1296,58 +1359,58 @@
         <v>33</v>
       </c>
       <c r="O8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P8" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q8" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="R8" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="S8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="U8" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="V8" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="W8" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="X8">
-        <v>300</v>
+        <v>3773</v>
       </c>
       <c r="Y8">
-        <v>62000</v>
+        <v>92722</v>
       </c>
       <c r="Z8">
         <v>0</v>
       </c>
       <c r="AA8" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="AB8" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="AC8" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="AD8">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>3773</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>3773</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1358,37 +1421,37 @@
         <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H9" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="I9" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="J9" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="K9">
-        <v>11000</v>
+        <v>8444</v>
       </c>
       <c r="L9">
-        <v>62000</v>
+        <v>92722</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -1397,58 +1460,58 @@
         <v>33</v>
       </c>
       <c r="O9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P9" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="R9" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="S9" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T9" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="U9" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="V9" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="W9" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="X9">
-        <v>11000</v>
+        <v>8444</v>
       </c>
       <c r="Y9">
-        <v>62000</v>
+        <v>92722</v>
       </c>
       <c r="Z9">
         <v>0</v>
       </c>
       <c r="AA9" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="AB9" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="AC9" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="AD9">
         <v>0</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>8444</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>8444</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
@@ -1456,100 +1519,100 @@
     </row>
     <row r="10" spans="1:33">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10">
+        <v>19870</v>
+      </c>
+      <c r="L10">
+        <v>92722</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
         <v>34</v>
       </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="O10" t="s">
         <v>38</v>
       </c>
-      <c r="G10" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" t="s">
-        <v>39</v>
-      </c>
-      <c r="I10" t="s">
-        <v>39</v>
-      </c>
-      <c r="J10" t="s">
-        <v>48</v>
-      </c>
-      <c r="K10">
-        <v>2750</v>
-      </c>
-      <c r="L10">
-        <v>62000</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>33</v>
-      </c>
-      <c r="O10" t="s">
-        <v>34</v>
-      </c>
       <c r="P10" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q10" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="R10" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="S10" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T10" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="U10" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="V10" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="W10" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="X10">
-        <v>2750</v>
+        <v>19870</v>
       </c>
       <c r="Y10">
-        <v>62000</v>
+        <v>92722</v>
       </c>
       <c r="Z10">
         <v>0</v>
       </c>
       <c r="AA10" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="AB10" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="AC10" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="AD10">
-        <v>2750</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>19870</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>19870</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
@@ -1557,100 +1620,100 @@
     </row>
     <row r="11" spans="1:33">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" t="s">
+        <v>51</v>
+      </c>
+      <c r="J11" t="s">
+        <v>58</v>
+      </c>
+      <c r="K11">
+        <v>3773</v>
+      </c>
+      <c r="L11">
+        <v>92722</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
         <v>34</v>
       </c>
-      <c r="C11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="O11" t="s">
         <v>38</v>
       </c>
-      <c r="G11" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11" t="s">
-        <v>39</v>
-      </c>
-      <c r="J11" t="s">
-        <v>49</v>
-      </c>
-      <c r="K11">
-        <v>3600</v>
-      </c>
-      <c r="L11">
-        <v>62000</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>33</v>
-      </c>
-      <c r="O11" t="s">
-        <v>34</v>
-      </c>
       <c r="P11" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q11" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="R11" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="S11" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T11" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="U11" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="V11" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="W11" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="X11">
-        <v>3600</v>
+        <v>3773</v>
       </c>
       <c r="Y11">
-        <v>62000</v>
+        <v>92722</v>
       </c>
       <c r="Z11">
         <v>0</v>
       </c>
       <c r="AA11" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="AB11" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="AC11" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>3773</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>3773</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>3773</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1658,100 +1721,100 @@
     </row>
     <row r="12" spans="1:33">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" t="s">
+        <v>57</v>
+      </c>
+      <c r="K12">
+        <v>10650</v>
+      </c>
+      <c r="L12">
+        <v>92722</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
         <v>34</v>
       </c>
-      <c r="C12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="O12" t="s">
         <v>38</v>
       </c>
-      <c r="G12" t="s">
-        <v>38</v>
-      </c>
-      <c r="H12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J12" t="s">
-        <v>50</v>
-      </c>
-      <c r="K12">
-        <v>5500</v>
-      </c>
-      <c r="L12">
-        <v>62000</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>33</v>
-      </c>
-      <c r="O12" t="s">
-        <v>34</v>
-      </c>
       <c r="P12" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q12" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="R12" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="S12" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T12" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="U12" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="V12" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="W12" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="X12">
-        <v>5500</v>
+        <v>10650</v>
       </c>
       <c r="Y12">
-        <v>62000</v>
+        <v>92722</v>
       </c>
       <c r="Z12">
         <v>0</v>
       </c>
       <c r="AA12" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="AB12" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="AC12" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="AD12">
-        <v>5500</v>
+        <v>10650</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>10650</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>10650</v>
       </c>
       <c r="AG12" t="b">
         <v>0</v>
@@ -1759,100 +1822,100 @@
     </row>
     <row r="13" spans="1:33">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" t="s">
+        <v>51</v>
+      </c>
+      <c r="I13" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" t="s">
+        <v>54</v>
+      </c>
+      <c r="K13">
+        <v>19702</v>
+      </c>
+      <c r="L13">
+        <v>92722</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
         <v>34</v>
       </c>
-      <c r="C13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="O13" t="s">
         <v>38</v>
       </c>
-      <c r="G13" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13" t="s">
-        <v>39</v>
-      </c>
-      <c r="I13" t="s">
-        <v>39</v>
-      </c>
-      <c r="J13" t="s">
-        <v>51</v>
-      </c>
-      <c r="K13">
-        <v>150</v>
-      </c>
-      <c r="L13">
-        <v>62000</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>33</v>
-      </c>
-      <c r="O13" t="s">
-        <v>34</v>
-      </c>
       <c r="P13" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q13" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="R13" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="S13" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T13" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="U13" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="V13" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="W13" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="X13">
-        <v>150</v>
+        <v>19702</v>
       </c>
       <c r="Y13">
-        <v>62000</v>
+        <v>92722</v>
       </c>
       <c r="Z13">
         <v>0</v>
       </c>
       <c r="AA13" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="AB13" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="AC13" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>19702</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>19702</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>19702</v>
       </c>
       <c r="AG13" t="b">
         <v>0</v>
@@ -1860,100 +1923,100 @@
     </row>
     <row r="14" spans="1:33">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" t="s">
+        <v>51</v>
+      </c>
+      <c r="I14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J14" t="s">
+        <v>55</v>
+      </c>
+      <c r="K14">
+        <v>2138</v>
+      </c>
+      <c r="L14">
+        <v>92722</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
         <v>34</v>
       </c>
-      <c r="C14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="O14" t="s">
         <v>38</v>
       </c>
-      <c r="G14" t="s">
-        <v>38</v>
-      </c>
-      <c r="H14" t="s">
-        <v>39</v>
-      </c>
-      <c r="I14" t="s">
-        <v>39</v>
-      </c>
-      <c r="J14" t="s">
-        <v>52</v>
-      </c>
-      <c r="K14">
-        <v>600</v>
-      </c>
-      <c r="L14">
-        <v>62000</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14" t="s">
-        <v>33</v>
-      </c>
-      <c r="O14" t="s">
-        <v>34</v>
-      </c>
       <c r="P14" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q14" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="R14" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="S14" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T14" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="U14" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="V14" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="W14" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="X14">
-        <v>600</v>
+        <v>2138</v>
       </c>
       <c r="Y14">
-        <v>62000</v>
+        <v>92722</v>
       </c>
       <c r="Z14">
         <v>0</v>
       </c>
       <c r="AA14" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="AB14" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="AC14" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="AD14">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>2138</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>2138</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
@@ -1961,102 +2024,2930 @@
     </row>
     <row r="15" spans="1:33">
       <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15" t="s">
+        <v>51</v>
+      </c>
+      <c r="I15" t="s">
+        <v>51</v>
+      </c>
+      <c r="J15" t="s">
+        <v>59</v>
+      </c>
+      <c r="K15">
+        <v>8444</v>
+      </c>
+      <c r="L15">
+        <v>92722</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>34</v>
+      </c>
+      <c r="O15" t="s">
+        <v>38</v>
+      </c>
+      <c r="P15" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>45</v>
+      </c>
+      <c r="R15" t="s">
+        <v>48</v>
+      </c>
+      <c r="S15" t="s">
+        <v>50</v>
+      </c>
+      <c r="T15" t="s">
+        <v>50</v>
+      </c>
+      <c r="U15" t="s">
+        <v>51</v>
+      </c>
+      <c r="V15" t="s">
+        <v>51</v>
+      </c>
+      <c r="W15" t="s">
+        <v>59</v>
+      </c>
+      <c r="X15">
+        <v>8444</v>
+      </c>
+      <c r="Y15">
+        <v>92722</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD15">
+        <v>8444</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" t="s">
+        <v>51</v>
+      </c>
+      <c r="I16" t="s">
+        <v>51</v>
+      </c>
+      <c r="J16" t="s">
+        <v>52</v>
+      </c>
+      <c r="K16">
+        <v>16887</v>
+      </c>
+      <c r="L16">
+        <v>92722</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>34</v>
+      </c>
+      <c r="O16" t="s">
+        <v>38</v>
+      </c>
+      <c r="P16" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>45</v>
+      </c>
+      <c r="R16" t="s">
+        <v>48</v>
+      </c>
+      <c r="S16" t="s">
+        <v>50</v>
+      </c>
+      <c r="T16" t="s">
+        <v>50</v>
+      </c>
+      <c r="U16" t="s">
+        <v>51</v>
+      </c>
+      <c r="V16" t="s">
+        <v>51</v>
+      </c>
+      <c r="W16" t="s">
+        <v>52</v>
+      </c>
+      <c r="X16">
+        <v>16887</v>
+      </c>
+      <c r="Y16">
+        <v>92722</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD16">
+        <v>16887</v>
+      </c>
+      <c r="AE16">
+        <v>16887</v>
+      </c>
+      <c r="AF16">
+        <v>16887</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17" t="s">
+        <v>51</v>
+      </c>
+      <c r="I17" t="s">
+        <v>51</v>
+      </c>
+      <c r="J17" t="s">
+        <v>56</v>
+      </c>
+      <c r="K17">
+        <v>11258</v>
+      </c>
+      <c r="L17">
+        <v>92722</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>34</v>
+      </c>
+      <c r="O17" t="s">
+        <v>38</v>
+      </c>
+      <c r="P17" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>45</v>
+      </c>
+      <c r="R17" t="s">
+        <v>48</v>
+      </c>
+      <c r="S17" t="s">
+        <v>50</v>
+      </c>
+      <c r="T17" t="s">
+        <v>50</v>
+      </c>
+      <c r="U17" t="s">
+        <v>51</v>
+      </c>
+      <c r="V17" t="s">
+        <v>51</v>
+      </c>
+      <c r="W17" t="s">
+        <v>56</v>
+      </c>
+      <c r="X17">
+        <v>11258</v>
+      </c>
+      <c r="Y17">
+        <v>92722</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD17">
+        <v>11258</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18" t="s">
+        <v>50</v>
+      </c>
+      <c r="H18" t="s">
+        <v>51</v>
+      </c>
+      <c r="I18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J18" t="s">
+        <v>53</v>
+      </c>
+      <c r="K18">
+        <v>19870</v>
+      </c>
+      <c r="L18">
+        <v>92722</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>35</v>
+      </c>
+      <c r="O18" t="s">
+        <v>39</v>
+      </c>
+      <c r="P18" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>46</v>
+      </c>
+      <c r="R18" t="s">
+        <v>48</v>
+      </c>
+      <c r="S18" t="s">
+        <v>50</v>
+      </c>
+      <c r="T18" t="s">
+        <v>50</v>
+      </c>
+      <c r="U18" t="s">
+        <v>51</v>
+      </c>
+      <c r="V18" t="s">
+        <v>51</v>
+      </c>
+      <c r="W18" t="s">
+        <v>53</v>
+      </c>
+      <c r="X18">
+        <v>19870</v>
+      </c>
+      <c r="Y18">
+        <v>92722</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>19870</v>
+      </c>
+      <c r="AF18">
+        <v>19870</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" t="s">
+        <v>50</v>
+      </c>
+      <c r="G19" t="s">
+        <v>50</v>
+      </c>
+      <c r="H19" t="s">
+        <v>51</v>
+      </c>
+      <c r="I19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J19" t="s">
+        <v>55</v>
+      </c>
+      <c r="K19">
+        <v>2138</v>
+      </c>
+      <c r="L19">
+        <v>92722</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>35</v>
+      </c>
+      <c r="O19" t="s">
+        <v>39</v>
+      </c>
+      <c r="P19" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>46</v>
+      </c>
+      <c r="R19" t="s">
+        <v>48</v>
+      </c>
+      <c r="S19" t="s">
+        <v>50</v>
+      </c>
+      <c r="T19" t="s">
+        <v>50</v>
+      </c>
+      <c r="U19" t="s">
+        <v>51</v>
+      </c>
+      <c r="V19" t="s">
+        <v>51</v>
+      </c>
+      <c r="W19" t="s">
+        <v>55</v>
+      </c>
+      <c r="X19">
+        <v>2138</v>
+      </c>
+      <c r="Y19">
+        <v>92722</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>2138</v>
+      </c>
+      <c r="AF19">
+        <v>2138</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" t="s">
+        <v>50</v>
+      </c>
+      <c r="G20" t="s">
+        <v>50</v>
+      </c>
+      <c r="H20" t="s">
+        <v>51</v>
+      </c>
+      <c r="I20" t="s">
+        <v>51</v>
+      </c>
+      <c r="J20" t="s">
+        <v>58</v>
+      </c>
+      <c r="K20">
+        <v>3773</v>
+      </c>
+      <c r="L20">
+        <v>92722</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>35</v>
+      </c>
+      <c r="O20" t="s">
+        <v>39</v>
+      </c>
+      <c r="P20" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R20" t="s">
+        <v>48</v>
+      </c>
+      <c r="S20" t="s">
+        <v>50</v>
+      </c>
+      <c r="T20" t="s">
+        <v>50</v>
+      </c>
+      <c r="U20" t="s">
+        <v>51</v>
+      </c>
+      <c r="V20" t="s">
+        <v>51</v>
+      </c>
+      <c r="W20" t="s">
+        <v>58</v>
+      </c>
+      <c r="X20">
+        <v>3773</v>
+      </c>
+      <c r="Y20">
+        <v>92722</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>3773</v>
+      </c>
+      <c r="AF20">
+        <v>3773</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21" t="s">
+        <v>51</v>
+      </c>
+      <c r="I21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J21" t="s">
+        <v>57</v>
+      </c>
+      <c r="K21">
+        <v>10650</v>
+      </c>
+      <c r="L21">
+        <v>92722</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>35</v>
+      </c>
+      <c r="O21" t="s">
+        <v>39</v>
+      </c>
+      <c r="P21" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>46</v>
+      </c>
+      <c r="R21" t="s">
+        <v>48</v>
+      </c>
+      <c r="S21" t="s">
+        <v>50</v>
+      </c>
+      <c r="T21" t="s">
+        <v>50</v>
+      </c>
+      <c r="U21" t="s">
+        <v>51</v>
+      </c>
+      <c r="V21" t="s">
+        <v>51</v>
+      </c>
+      <c r="W21" t="s">
+        <v>57</v>
+      </c>
+      <c r="X21">
+        <v>10650</v>
+      </c>
+      <c r="Y21">
+        <v>92722</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>10650</v>
+      </c>
+      <c r="AF21">
+        <v>10650</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" t="s">
+        <v>50</v>
+      </c>
+      <c r="G22" t="s">
+        <v>50</v>
+      </c>
+      <c r="H22" t="s">
+        <v>51</v>
+      </c>
+      <c r="I22" t="s">
+        <v>51</v>
+      </c>
+      <c r="J22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K22">
+        <v>8444</v>
+      </c>
+      <c r="L22">
+        <v>92722</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>35</v>
+      </c>
+      <c r="O22" t="s">
+        <v>39</v>
+      </c>
+      <c r="P22" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>46</v>
+      </c>
+      <c r="R22" t="s">
+        <v>48</v>
+      </c>
+      <c r="S22" t="s">
+        <v>50</v>
+      </c>
+      <c r="T22" t="s">
+        <v>50</v>
+      </c>
+      <c r="U22" t="s">
+        <v>51</v>
+      </c>
+      <c r="V22" t="s">
+        <v>51</v>
+      </c>
+      <c r="W22" t="s">
+        <v>59</v>
+      </c>
+      <c r="X22">
+        <v>8444</v>
+      </c>
+      <c r="Y22">
+        <v>92722</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD22">
+        <v>8444</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" t="s">
+        <v>50</v>
+      </c>
+      <c r="G23" t="s">
+        <v>50</v>
+      </c>
+      <c r="H23" t="s">
+        <v>51</v>
+      </c>
+      <c r="I23" t="s">
+        <v>51</v>
+      </c>
+      <c r="J23" t="s">
+        <v>52</v>
+      </c>
+      <c r="K23">
+        <v>16887</v>
+      </c>
+      <c r="L23">
+        <v>92722</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>35</v>
+      </c>
+      <c r="O23" t="s">
+        <v>39</v>
+      </c>
+      <c r="P23" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R23" t="s">
+        <v>48</v>
+      </c>
+      <c r="S23" t="s">
+        <v>50</v>
+      </c>
+      <c r="T23" t="s">
+        <v>50</v>
+      </c>
+      <c r="U23" t="s">
+        <v>51</v>
+      </c>
+      <c r="V23" t="s">
+        <v>51</v>
+      </c>
+      <c r="W23" t="s">
+        <v>52</v>
+      </c>
+      <c r="X23">
+        <v>16887</v>
+      </c>
+      <c r="Y23">
+        <v>92722</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD23">
+        <v>16887</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33">
+      <c r="A24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" t="s">
+        <v>50</v>
+      </c>
+      <c r="H24" t="s">
+        <v>51</v>
+      </c>
+      <c r="I24" t="s">
+        <v>51</v>
+      </c>
+      <c r="J24" t="s">
+        <v>54</v>
+      </c>
+      <c r="K24">
+        <v>19702</v>
+      </c>
+      <c r="L24">
+        <v>92722</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>35</v>
+      </c>
+      <c r="O24" t="s">
+        <v>39</v>
+      </c>
+      <c r="P24" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>46</v>
+      </c>
+      <c r="R24" t="s">
+        <v>48</v>
+      </c>
+      <c r="S24" t="s">
+        <v>50</v>
+      </c>
+      <c r="T24" t="s">
+        <v>50</v>
+      </c>
+      <c r="U24" t="s">
+        <v>51</v>
+      </c>
+      <c r="V24" t="s">
+        <v>51</v>
+      </c>
+      <c r="W24" t="s">
+        <v>54</v>
+      </c>
+      <c r="X24">
+        <v>19702</v>
+      </c>
+      <c r="Y24">
+        <v>92722</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD24">
+        <v>19702</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33">
+      <c r="A25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" t="s">
+        <v>50</v>
+      </c>
+      <c r="G25" t="s">
+        <v>50</v>
+      </c>
+      <c r="H25" t="s">
+        <v>51</v>
+      </c>
+      <c r="I25" t="s">
+        <v>51</v>
+      </c>
+      <c r="J25" t="s">
+        <v>56</v>
+      </c>
+      <c r="K25">
+        <v>11258</v>
+      </c>
+      <c r="L25">
+        <v>92722</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>35</v>
+      </c>
+      <c r="O25" t="s">
+        <v>39</v>
+      </c>
+      <c r="P25" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R25" t="s">
+        <v>48</v>
+      </c>
+      <c r="S25" t="s">
+        <v>50</v>
+      </c>
+      <c r="T25" t="s">
+        <v>50</v>
+      </c>
+      <c r="U25" t="s">
+        <v>51</v>
+      </c>
+      <c r="V25" t="s">
+        <v>51</v>
+      </c>
+      <c r="W25" t="s">
+        <v>56</v>
+      </c>
+      <c r="X25">
+        <v>11258</v>
+      </c>
+      <c r="Y25">
+        <v>92722</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD25">
+        <v>11258</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" t="s">
+        <v>47</v>
+      </c>
+      <c r="E26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" t="s">
+        <v>50</v>
+      </c>
+      <c r="G26" t="s">
+        <v>50</v>
+      </c>
+      <c r="H26" t="s">
+        <v>51</v>
+      </c>
+      <c r="I26" t="s">
+        <v>51</v>
+      </c>
+      <c r="J26" t="s">
+        <v>59</v>
+      </c>
+      <c r="K26">
+        <v>8444</v>
+      </c>
+      <c r="L26">
+        <v>92722</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>36</v>
+      </c>
+      <c r="O26" t="s">
+        <v>40</v>
+      </c>
+      <c r="P26" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>47</v>
+      </c>
+      <c r="R26" t="s">
+        <v>48</v>
+      </c>
+      <c r="S26" t="s">
+        <v>50</v>
+      </c>
+      <c r="T26" t="s">
+        <v>50</v>
+      </c>
+      <c r="U26" t="s">
+        <v>51</v>
+      </c>
+      <c r="V26" t="s">
+        <v>51</v>
+      </c>
+      <c r="W26" t="s">
+        <v>59</v>
+      </c>
+      <c r="X26">
+        <v>8444</v>
+      </c>
+      <c r="Y26">
+        <v>92722</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD26">
+        <v>8444</v>
+      </c>
+      <c r="AE26">
+        <v>8444</v>
+      </c>
+      <c r="AF26">
+        <v>8444</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" t="s">
+        <v>50</v>
+      </c>
+      <c r="H27" t="s">
+        <v>51</v>
+      </c>
+      <c r="I27" t="s">
+        <v>51</v>
+      </c>
+      <c r="J27" t="s">
+        <v>52</v>
+      </c>
+      <c r="K27">
+        <v>16887</v>
+      </c>
+      <c r="L27">
+        <v>92722</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>36</v>
+      </c>
+      <c r="O27" t="s">
+        <v>40</v>
+      </c>
+      <c r="P27" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>47</v>
+      </c>
+      <c r="R27" t="s">
+        <v>48</v>
+      </c>
+      <c r="S27" t="s">
+        <v>50</v>
+      </c>
+      <c r="T27" t="s">
+        <v>50</v>
+      </c>
+      <c r="U27" t="s">
+        <v>51</v>
+      </c>
+      <c r="V27" t="s">
+        <v>51</v>
+      </c>
+      <c r="W27" t="s">
+        <v>52</v>
+      </c>
+      <c r="X27">
+        <v>16887</v>
+      </c>
+      <c r="Y27">
+        <v>92722</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD27">
+        <v>16887</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" t="s">
+        <v>50</v>
+      </c>
+      <c r="G28" t="s">
+        <v>50</v>
+      </c>
+      <c r="H28" t="s">
+        <v>51</v>
+      </c>
+      <c r="I28" t="s">
+        <v>51</v>
+      </c>
+      <c r="J28" t="s">
+        <v>57</v>
+      </c>
+      <c r="K28">
+        <v>10650</v>
+      </c>
+      <c r="L28">
+        <v>92722</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>36</v>
+      </c>
+      <c r="O28" t="s">
+        <v>40</v>
+      </c>
+      <c r="P28" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>47</v>
+      </c>
+      <c r="R28" t="s">
+        <v>48</v>
+      </c>
+      <c r="S28" t="s">
+        <v>50</v>
+      </c>
+      <c r="T28" t="s">
+        <v>50</v>
+      </c>
+      <c r="U28" t="s">
+        <v>51</v>
+      </c>
+      <c r="V28" t="s">
+        <v>51</v>
+      </c>
+      <c r="W28" t="s">
+        <v>57</v>
+      </c>
+      <c r="X28">
+        <v>10650</v>
+      </c>
+      <c r="Y28">
+        <v>92722</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>10650</v>
+      </c>
+      <c r="AF28">
+        <v>10650</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" t="s">
+        <v>50</v>
+      </c>
+      <c r="G29" t="s">
+        <v>50</v>
+      </c>
+      <c r="H29" t="s">
+        <v>51</v>
+      </c>
+      <c r="I29" t="s">
+        <v>51</v>
+      </c>
+      <c r="J29" t="s">
+        <v>55</v>
+      </c>
+      <c r="K29">
+        <v>2138</v>
+      </c>
+      <c r="L29">
+        <v>92722</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>36</v>
+      </c>
+      <c r="O29" t="s">
+        <v>40</v>
+      </c>
+      <c r="P29" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>47</v>
+      </c>
+      <c r="R29" t="s">
+        <v>48</v>
+      </c>
+      <c r="S29" t="s">
+        <v>50</v>
+      </c>
+      <c r="T29" t="s">
+        <v>50</v>
+      </c>
+      <c r="U29" t="s">
+        <v>51</v>
+      </c>
+      <c r="V29" t="s">
+        <v>51</v>
+      </c>
+      <c r="W29" t="s">
+        <v>55</v>
+      </c>
+      <c r="X29">
+        <v>2138</v>
+      </c>
+      <c r="Y29">
+        <v>92722</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD29">
+        <v>2138</v>
+      </c>
+      <c r="AE29">
+        <v>2138</v>
+      </c>
+      <c r="AF29">
+        <v>2138</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33">
+      <c r="A30" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" t="s">
+        <v>48</v>
+      </c>
+      <c r="F30" t="s">
+        <v>50</v>
+      </c>
+      <c r="G30" t="s">
+        <v>50</v>
+      </c>
+      <c r="H30" t="s">
+        <v>51</v>
+      </c>
+      <c r="I30" t="s">
+        <v>51</v>
+      </c>
+      <c r="J30" t="s">
+        <v>53</v>
+      </c>
+      <c r="K30">
+        <v>19870</v>
+      </c>
+      <c r="L30">
+        <v>92722</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>36</v>
+      </c>
+      <c r="O30" t="s">
+        <v>40</v>
+      </c>
+      <c r="P30" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>47</v>
+      </c>
+      <c r="R30" t="s">
+        <v>48</v>
+      </c>
+      <c r="S30" t="s">
+        <v>50</v>
+      </c>
+      <c r="T30" t="s">
+        <v>50</v>
+      </c>
+      <c r="U30" t="s">
+        <v>51</v>
+      </c>
+      <c r="V30" t="s">
+        <v>51</v>
+      </c>
+      <c r="W30" t="s">
+        <v>53</v>
+      </c>
+      <c r="X30">
+        <v>19870</v>
+      </c>
+      <c r="Y30">
+        <v>92722</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD30">
+        <v>19870</v>
+      </c>
+      <c r="AE30">
+        <v>19870</v>
+      </c>
+      <c r="AF30">
+        <v>19870</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31" t="s">
+        <v>48</v>
+      </c>
+      <c r="F31" t="s">
+        <v>50</v>
+      </c>
+      <c r="G31" t="s">
+        <v>50</v>
+      </c>
+      <c r="H31" t="s">
+        <v>51</v>
+      </c>
+      <c r="I31" t="s">
+        <v>51</v>
+      </c>
+      <c r="J31" t="s">
+        <v>54</v>
+      </c>
+      <c r="K31">
+        <v>19702</v>
+      </c>
+      <c r="L31">
+        <v>92722</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="s">
+        <v>36</v>
+      </c>
+      <c r="O31" t="s">
+        <v>40</v>
+      </c>
+      <c r="P31" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>47</v>
+      </c>
+      <c r="R31" t="s">
+        <v>48</v>
+      </c>
+      <c r="S31" t="s">
+        <v>50</v>
+      </c>
+      <c r="T31" t="s">
+        <v>50</v>
+      </c>
+      <c r="U31" t="s">
+        <v>51</v>
+      </c>
+      <c r="V31" t="s">
+        <v>51</v>
+      </c>
+      <c r="W31" t="s">
+        <v>54</v>
+      </c>
+      <c r="X31">
+        <v>19702</v>
+      </c>
+      <c r="Y31">
+        <v>92722</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD31">
+        <v>19702</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" t="s">
+        <v>48</v>
+      </c>
+      <c r="F32" t="s">
+        <v>50</v>
+      </c>
+      <c r="G32" t="s">
+        <v>50</v>
+      </c>
+      <c r="H32" t="s">
+        <v>51</v>
+      </c>
+      <c r="I32" t="s">
+        <v>51</v>
+      </c>
+      <c r="J32" t="s">
+        <v>56</v>
+      </c>
+      <c r="K32">
+        <v>11258</v>
+      </c>
+      <c r="L32">
+        <v>92722</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
+        <v>36</v>
+      </c>
+      <c r="O32" t="s">
+        <v>40</v>
+      </c>
+      <c r="P32" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>47</v>
+      </c>
+      <c r="R32" t="s">
+        <v>48</v>
+      </c>
+      <c r="S32" t="s">
+        <v>50</v>
+      </c>
+      <c r="T32" t="s">
+        <v>50</v>
+      </c>
+      <c r="U32" t="s">
+        <v>51</v>
+      </c>
+      <c r="V32" t="s">
+        <v>51</v>
+      </c>
+      <c r="W32" t="s">
+        <v>56</v>
+      </c>
+      <c r="X32">
+        <v>11258</v>
+      </c>
+      <c r="Y32">
+        <v>92722</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD32">
+        <v>11258</v>
+      </c>
+      <c r="AE32">
+        <v>11258</v>
+      </c>
+      <c r="AF32">
+        <v>11258</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" t="s">
+        <v>48</v>
+      </c>
+      <c r="F33" t="s">
+        <v>50</v>
+      </c>
+      <c r="G33" t="s">
+        <v>50</v>
+      </c>
+      <c r="H33" t="s">
+        <v>51</v>
+      </c>
+      <c r="I33" t="s">
+        <v>51</v>
+      </c>
+      <c r="J33" t="s">
+        <v>58</v>
+      </c>
+      <c r="K33">
+        <v>3773</v>
+      </c>
+      <c r="L33">
+        <v>92722</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>36</v>
+      </c>
+      <c r="O33" t="s">
+        <v>40</v>
+      </c>
+      <c r="P33" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>47</v>
+      </c>
+      <c r="R33" t="s">
+        <v>48</v>
+      </c>
+      <c r="S33" t="s">
+        <v>50</v>
+      </c>
+      <c r="T33" t="s">
+        <v>50</v>
+      </c>
+      <c r="U33" t="s">
+        <v>51</v>
+      </c>
+      <c r="V33" t="s">
+        <v>51</v>
+      </c>
+      <c r="W33" t="s">
+        <v>58</v>
+      </c>
+      <c r="X33">
+        <v>3773</v>
+      </c>
+      <c r="Y33">
+        <v>92722</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <v>3773</v>
+      </c>
+      <c r="AF33">
+        <v>3773</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33">
+      <c r="A34" t="s">
         <v>33</v>
       </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" t="s">
-        <v>37</v>
-      </c>
-      <c r="F15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G15" t="s">
-        <v>38</v>
-      </c>
-      <c r="H15" t="s">
-        <v>39</v>
-      </c>
-      <c r="I15" t="s">
-        <v>39</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="B34" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" t="s">
+        <v>44</v>
+      </c>
+      <c r="E34" t="s">
+        <v>49</v>
+      </c>
+      <c r="F34" t="s">
+        <v>50</v>
+      </c>
+      <c r="G34" t="s">
+        <v>50</v>
+      </c>
+      <c r="H34" t="s">
+        <v>51</v>
+      </c>
+      <c r="I34" t="s">
+        <v>51</v>
+      </c>
+      <c r="J34" t="s">
+        <v>60</v>
+      </c>
+      <c r="K34">
+        <v>7493</v>
+      </c>
+      <c r="L34">
+        <v>82484</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>33</v>
+      </c>
+      <c r="O34" t="s">
+        <v>41</v>
+      </c>
+      <c r="P34" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>44</v>
+      </c>
+      <c r="R34" t="s">
+        <v>49</v>
+      </c>
+      <c r="S34" t="s">
+        <v>50</v>
+      </c>
+      <c r="T34" t="s">
+        <v>50</v>
+      </c>
+      <c r="U34" t="s">
+        <v>51</v>
+      </c>
+      <c r="V34" t="s">
+        <v>51</v>
+      </c>
+      <c r="W34" t="s">
+        <v>60</v>
+      </c>
+      <c r="X34">
+        <v>7493</v>
+      </c>
+      <c r="Y34">
+        <v>82484</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>7493</v>
+      </c>
+      <c r="AF34">
+        <v>7493</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33">
+      <c r="A35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" t="s">
+        <v>44</v>
+      </c>
+      <c r="E35" t="s">
+        <v>49</v>
+      </c>
+      <c r="F35" t="s">
+        <v>50</v>
+      </c>
+      <c r="G35" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" t="s">
+        <v>51</v>
+      </c>
+      <c r="J35" t="s">
+        <v>58</v>
+      </c>
+      <c r="K35">
+        <v>803</v>
+      </c>
+      <c r="L35">
+        <v>82484</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35" t="s">
+        <v>33</v>
+      </c>
+      <c r="O35" t="s">
+        <v>41</v>
+      </c>
+      <c r="P35" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>44</v>
+      </c>
+      <c r="R35" t="s">
+        <v>49</v>
+      </c>
+      <c r="S35" t="s">
+        <v>50</v>
+      </c>
+      <c r="T35" t="s">
+        <v>50</v>
+      </c>
+      <c r="U35" t="s">
+        <v>51</v>
+      </c>
+      <c r="V35" t="s">
+        <v>51</v>
+      </c>
+      <c r="W35" t="s">
+        <v>58</v>
+      </c>
+      <c r="X35">
+        <v>803</v>
+      </c>
+      <c r="Y35">
+        <v>82484</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
+      <c r="AE35">
+        <v>803</v>
+      </c>
+      <c r="AF35">
+        <v>803</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33">
+      <c r="A36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" t="s">
+        <v>49</v>
+      </c>
+      <c r="F36" t="s">
+        <v>50</v>
+      </c>
+      <c r="G36" t="s">
+        <v>50</v>
+      </c>
+      <c r="H36" t="s">
+        <v>51</v>
+      </c>
+      <c r="I36" t="s">
+        <v>51</v>
+      </c>
+      <c r="J36" t="s">
+        <v>61</v>
+      </c>
+      <c r="K36">
+        <v>191</v>
+      </c>
+      <c r="L36">
+        <v>82484</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36" t="s">
+        <v>33</v>
+      </c>
+      <c r="O36" t="s">
+        <v>41</v>
+      </c>
+      <c r="P36" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>44</v>
+      </c>
+      <c r="R36" t="s">
+        <v>49</v>
+      </c>
+      <c r="S36" t="s">
+        <v>50</v>
+      </c>
+      <c r="T36" t="s">
+        <v>50</v>
+      </c>
+      <c r="U36" t="s">
+        <v>51</v>
+      </c>
+      <c r="V36" t="s">
+        <v>51</v>
+      </c>
+      <c r="W36" t="s">
+        <v>61</v>
+      </c>
+      <c r="X36">
+        <v>191</v>
+      </c>
+      <c r="Y36">
+        <v>82484</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>191</v>
+      </c>
+      <c r="AF36">
+        <v>191</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33">
+      <c r="A37" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" t="s">
+        <v>50</v>
+      </c>
+      <c r="G37" t="s">
+        <v>50</v>
+      </c>
+      <c r="H37" t="s">
+        <v>51</v>
+      </c>
+      <c r="I37" t="s">
+        <v>51</v>
+      </c>
+      <c r="J37" t="s">
+        <v>62</v>
+      </c>
+      <c r="K37">
+        <v>3747</v>
+      </c>
+      <c r="L37">
+        <v>82484</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" t="s">
+        <v>33</v>
+      </c>
+      <c r="O37" t="s">
+        <v>41</v>
+      </c>
+      <c r="P37" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>44</v>
+      </c>
+      <c r="R37" t="s">
+        <v>49</v>
+      </c>
+      <c r="S37" t="s">
+        <v>50</v>
+      </c>
+      <c r="T37" t="s">
+        <v>50</v>
+      </c>
+      <c r="U37" t="s">
+        <v>51</v>
+      </c>
+      <c r="V37" t="s">
+        <v>51</v>
+      </c>
+      <c r="W37" t="s">
+        <v>62</v>
+      </c>
+      <c r="X37">
+        <v>3747</v>
+      </c>
+      <c r="Y37">
+        <v>82484</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <v>3747</v>
+      </c>
+      <c r="AF37">
+        <v>3747</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33">
+      <c r="A38" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" t="s">
+        <v>44</v>
+      </c>
+      <c r="E38" t="s">
+        <v>49</v>
+      </c>
+      <c r="F38" t="s">
+        <v>50</v>
+      </c>
+      <c r="G38" t="s">
+        <v>50</v>
+      </c>
+      <c r="H38" t="s">
+        <v>51</v>
+      </c>
+      <c r="I38" t="s">
+        <v>51</v>
+      </c>
+      <c r="J38" t="s">
+        <v>63</v>
+      </c>
+      <c r="K38">
+        <v>162</v>
+      </c>
+      <c r="L38">
+        <v>82484</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38" t="s">
+        <v>33</v>
+      </c>
+      <c r="O38" t="s">
+        <v>41</v>
+      </c>
+      <c r="P38" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>44</v>
+      </c>
+      <c r="R38" t="s">
+        <v>49</v>
+      </c>
+      <c r="S38" t="s">
+        <v>50</v>
+      </c>
+      <c r="T38" t="s">
+        <v>50</v>
+      </c>
+      <c r="U38" t="s">
+        <v>51</v>
+      </c>
+      <c r="V38" t="s">
+        <v>51</v>
+      </c>
+      <c r="W38" t="s">
+        <v>63</v>
+      </c>
+      <c r="X38">
+        <v>162</v>
+      </c>
+      <c r="Y38">
+        <v>82484</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>162</v>
+      </c>
+      <c r="AF38">
+        <v>162</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33">
+      <c r="A39" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D39" t="s">
+        <v>44</v>
+      </c>
+      <c r="E39" t="s">
+        <v>49</v>
+      </c>
+      <c r="F39" t="s">
+        <v>50</v>
+      </c>
+      <c r="G39" t="s">
+        <v>50</v>
+      </c>
+      <c r="H39" t="s">
+        <v>51</v>
+      </c>
+      <c r="I39" t="s">
+        <v>51</v>
+      </c>
+      <c r="J39" t="s">
+        <v>64</v>
+      </c>
+      <c r="K39">
+        <v>7493</v>
+      </c>
+      <c r="L39">
+        <v>82484</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>33</v>
+      </c>
+      <c r="O39" t="s">
+        <v>41</v>
+      </c>
+      <c r="P39" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>44</v>
+      </c>
+      <c r="R39" t="s">
+        <v>49</v>
+      </c>
+      <c r="S39" t="s">
+        <v>50</v>
+      </c>
+      <c r="T39" t="s">
+        <v>50</v>
+      </c>
+      <c r="U39" t="s">
+        <v>51</v>
+      </c>
+      <c r="V39" t="s">
+        <v>51</v>
+      </c>
+      <c r="W39" t="s">
+        <v>64</v>
+      </c>
+      <c r="X39">
+        <v>7493</v>
+      </c>
+      <c r="Y39">
+        <v>82484</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD39">
+        <v>0</v>
+      </c>
+      <c r="AE39">
+        <v>7493</v>
+      </c>
+      <c r="AF39">
+        <v>7493</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33">
+      <c r="A40" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" t="s">
+        <v>49</v>
+      </c>
+      <c r="F40" t="s">
+        <v>50</v>
+      </c>
+      <c r="G40" t="s">
+        <v>50</v>
+      </c>
+      <c r="H40" t="s">
+        <v>51</v>
+      </c>
+      <c r="I40" t="s">
+        <v>51</v>
+      </c>
+      <c r="J40" t="s">
+        <v>65</v>
+      </c>
+      <c r="K40">
+        <v>3747</v>
+      </c>
+      <c r="L40">
+        <v>82484</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40" t="s">
+        <v>33</v>
+      </c>
+      <c r="O40" t="s">
+        <v>41</v>
+      </c>
+      <c r="P40" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>44</v>
+      </c>
+      <c r="R40" t="s">
+        <v>49</v>
+      </c>
+      <c r="S40" t="s">
+        <v>50</v>
+      </c>
+      <c r="T40" t="s">
+        <v>50</v>
+      </c>
+      <c r="U40" t="s">
+        <v>51</v>
+      </c>
+      <c r="V40" t="s">
+        <v>51</v>
+      </c>
+      <c r="W40" t="s">
+        <v>65</v>
+      </c>
+      <c r="X40">
+        <v>3747</v>
+      </c>
+      <c r="Y40">
+        <v>82484</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD40">
+        <v>0</v>
+      </c>
+      <c r="AE40">
+        <v>3747</v>
+      </c>
+      <c r="AF40">
+        <v>3747</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33">
+      <c r="A41" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41" t="s">
+        <v>49</v>
+      </c>
+      <c r="F41" t="s">
+        <v>50</v>
+      </c>
+      <c r="G41" t="s">
+        <v>50</v>
+      </c>
+      <c r="H41" t="s">
+        <v>51</v>
+      </c>
+      <c r="I41" t="s">
+        <v>51</v>
+      </c>
+      <c r="J41" t="s">
+        <v>66</v>
+      </c>
+      <c r="K41">
+        <v>343</v>
+      </c>
+      <c r="L41">
+        <v>82484</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41" t="s">
+        <v>33</v>
+      </c>
+      <c r="O41" t="s">
+        <v>41</v>
+      </c>
+      <c r="P41" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>44</v>
+      </c>
+      <c r="R41" t="s">
+        <v>49</v>
+      </c>
+      <c r="S41" t="s">
+        <v>50</v>
+      </c>
+      <c r="T41" t="s">
+        <v>50</v>
+      </c>
+      <c r="U41" t="s">
+        <v>51</v>
+      </c>
+      <c r="V41" t="s">
+        <v>51</v>
+      </c>
+      <c r="W41" t="s">
+        <v>66</v>
+      </c>
+      <c r="X41">
+        <v>343</v>
+      </c>
+      <c r="Y41">
+        <v>82484</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD41">
+        <v>0</v>
+      </c>
+      <c r="AE41">
+        <v>343</v>
+      </c>
+      <c r="AF41">
+        <v>343</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:33">
+      <c r="A42" t="s">
+        <v>33</v>
+      </c>
+      <c r="B42" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" t="s">
+        <v>44</v>
+      </c>
+      <c r="E42" t="s">
+        <v>49</v>
+      </c>
+      <c r="F42" t="s">
+        <v>50</v>
+      </c>
+      <c r="G42" t="s">
+        <v>50</v>
+      </c>
+      <c r="H42" t="s">
+        <v>51</v>
+      </c>
+      <c r="I42" t="s">
+        <v>51</v>
+      </c>
+      <c r="J42" t="s">
         <v>53</v>
       </c>
-      <c r="K15">
-        <v>4950</v>
-      </c>
-      <c r="L15">
-        <v>62000</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
+      <c r="K42">
+        <v>6052</v>
+      </c>
+      <c r="L42">
+        <v>82484</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42" t="s">
         <v>33</v>
       </c>
-      <c r="O15" t="s">
-        <v>34</v>
-      </c>
-      <c r="P15" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>36</v>
-      </c>
-      <c r="R15" t="s">
-        <v>37</v>
-      </c>
-      <c r="S15" t="s">
-        <v>38</v>
-      </c>
-      <c r="T15" t="s">
-        <v>38</v>
-      </c>
-      <c r="U15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V15" t="s">
-        <v>39</v>
-      </c>
-      <c r="W15" t="s">
+      <c r="O42" t="s">
+        <v>41</v>
+      </c>
+      <c r="P42" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>44</v>
+      </c>
+      <c r="R42" t="s">
+        <v>49</v>
+      </c>
+      <c r="S42" t="s">
+        <v>50</v>
+      </c>
+      <c r="T42" t="s">
+        <v>50</v>
+      </c>
+      <c r="U42" t="s">
+        <v>51</v>
+      </c>
+      <c r="V42" t="s">
+        <v>51</v>
+      </c>
+      <c r="W42" t="s">
         <v>53</v>
       </c>
-      <c r="X15">
-        <v>4950</v>
-      </c>
-      <c r="Y15">
-        <v>62000</v>
-      </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>55</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>56</v>
-      </c>
-      <c r="AD15">
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
+      <c r="X42">
+        <v>6052</v>
+      </c>
+      <c r="Y42">
+        <v>82484</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD42">
+        <v>0</v>
+      </c>
+      <c r="AE42">
+        <v>6052</v>
+      </c>
+      <c r="AF42">
+        <v>6052</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:33">
+      <c r="A43" t="s">
+        <v>33</v>
+      </c>
+      <c r="B43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" t="s">
+        <v>43</v>
+      </c>
+      <c r="D43" t="s">
+        <v>44</v>
+      </c>
+      <c r="E43" t="s">
+        <v>49</v>
+      </c>
+      <c r="F43" t="s">
+        <v>50</v>
+      </c>
+      <c r="G43" t="s">
+        <v>50</v>
+      </c>
+      <c r="H43" t="s">
+        <v>51</v>
+      </c>
+      <c r="I43" t="s">
+        <v>51</v>
+      </c>
+      <c r="J43" t="s">
+        <v>67</v>
+      </c>
+      <c r="K43">
+        <v>52453</v>
+      </c>
+      <c r="L43">
+        <v>82484</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43" t="s">
+        <v>33</v>
+      </c>
+      <c r="O43" t="s">
+        <v>41</v>
+      </c>
+      <c r="P43" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>44</v>
+      </c>
+      <c r="R43" t="s">
+        <v>49</v>
+      </c>
+      <c r="S43" t="s">
+        <v>50</v>
+      </c>
+      <c r="T43" t="s">
+        <v>50</v>
+      </c>
+      <c r="U43" t="s">
+        <v>51</v>
+      </c>
+      <c r="V43" t="s">
+        <v>51</v>
+      </c>
+      <c r="W43" t="s">
+        <v>67</v>
+      </c>
+      <c r="X43">
+        <v>52453</v>
+      </c>
+      <c r="Y43">
+        <v>82484</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD43">
+        <v>0</v>
+      </c>
+      <c r="AE43">
+        <v>52453</v>
+      </c>
+      <c r="AF43">
+        <v>52453</v>
+      </c>
+      <c r="AG43" t="b">
         <v>0</v>
       </c>
     </row>
